--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:28</t>
+    <t xml:space="preserve">2026-09-24 01:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -818,19 +818,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="15">
@@ -841,19 +841,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>-0.03</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="16">
@@ -864,19 +864,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.17</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>-0.11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="17">
@@ -887,19 +887,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.36</v>
+        <v>0.1</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.38</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="18">
@@ -975,19 +975,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2" t="n">
         <v>-0.18</v>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>-0.19</v>
-      </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="22">
@@ -998,19 +998,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>-0.19</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="23">
@@ -1021,19 +1021,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>-0.11</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="24">
@@ -1044,19 +1044,19 @@
         <v>31</v>
       </c>
       <c r="C24" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>343</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="25">
@@ -1067,19 +1067,19 @@
         <v>31</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="26">
@@ -1093,13 +1093,13 @@
         <v>-0.9</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0.25</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>-1.15</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:18</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2021_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
